--- a/public/crawlability-zoolu-september-2026.xlsx
+++ b/public/crawlability-zoolu-september-2026.xlsx
@@ -24660,7 +24660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K263"/>
+  <dimension ref="A1:K183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -29239,7 +29239,7 @@
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=קליפי</t>
+          <t>https://zoolu.co.il/product-category/משחקים-וצעצועים-קבוצת-מילטין/</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -29247,7 +29247,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>לא נבדק</t>
+          <t>429 -&gt; 200</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr"/>
@@ -29257,241 +29257,7 @@
       <c r="F92" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J92" s="2" t="inlineStr"/>
-      <c r="K92" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גמון</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr"/>
-      <c r="E93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J93" s="2" t="inlineStr"/>
-      <c r="K93" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=אסטור</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr"/>
-      <c r="E94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J94" s="2" t="inlineStr"/>
-      <c r="K94" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=אקזוטרה</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr"/>
-      <c r="E95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J95" s="2" t="inlineStr"/>
-      <c r="K95" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=לרוי-laroy</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr"/>
-      <c r="E96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F96" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J96" s="2" t="inlineStr"/>
-      <c r="K96" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פרקטיקט</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr"/>
-      <c r="E97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="inlineStr"/>
-      <c r="K97" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/משחקים-וצעצועים-קבוצת-מילטין/</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>429 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr"/>
-      <c r="E98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G98" s="5" t="inlineStr">
+      <c r="G92" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -29506,45 +29272,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J98" s="2" t="inlineStr"/>
-      <c r="K98" s="6" t="inlineStr">
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="5" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/קולרים-קבוצת-מילטין/</t>
         </is>
       </c>
-      <c r="B99" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
+      <c r="B93" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr"/>
-      <c r="E99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" s="2" t="n">
+      <c r="D93" s="2" t="inlineStr"/>
+      <c r="E93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G99" s="5" t="inlineStr">
+      <c r="G93" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -29559,123 +29325,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr">
+      <c r="I93" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr"/>
-      <c r="K99" s="6" t="inlineStr">
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פטסייף</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr"/>
-      <c r="E100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" s="2" t="n">
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/אבני-אוויר-קבוצת-מילטין/</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>429 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr"/>
+      <c r="E94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J100" s="2" t="inlineStr"/>
-      <c r="K100" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=קטס-גריי</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr"/>
-      <c r="E101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J101" s="2" t="inlineStr"/>
-      <c r="K101" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/אבני-אוויר-קבוצת-מילטין/</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>429 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr"/>
-      <c r="E102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G102" s="5" t="inlineStr">
+      <c r="G94" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -29690,123 +29378,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J102" s="2" t="inlineStr"/>
-      <c r="K102" s="6" t="inlineStr">
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פרסטיג-prestige</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr"/>
-      <c r="E103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F103" s="2" t="n">
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/חטיפים-ושלוקים-קבוצת-מילטין/</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>429 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr"/>
+      <c r="E95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="inlineStr"/>
-      <c r="K103" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=אליזבת</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr"/>
-      <c r="E104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J104" s="2" t="inlineStr"/>
-      <c r="K104" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=foshan-verab</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr"/>
-      <c r="E105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G105" s="5" t="inlineStr">
+      <c r="G95" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -29821,240 +29431,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J105" s="2" t="inlineStr"/>
-      <c r="K105" s="6" t="inlineStr">
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ריפלקס</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr"/>
-      <c r="E106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F106" s="2" t="n">
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/שירותים/</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>429 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr"/>
+      <c r="E96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J106" s="2" t="inlineStr"/>
-      <c r="K106" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=בונזו-bonzo</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr"/>
-      <c r="E107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F107" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J107" s="2" t="inlineStr"/>
-      <c r="K107" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=קטרליטר</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr"/>
-      <c r="E108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F108" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J108" s="2" t="inlineStr"/>
-      <c r="K108" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=אקאנה-acana</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr"/>
-      <c r="E109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F109" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J109" s="2" t="inlineStr"/>
-      <c r="K109" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גוסידוג</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr"/>
-      <c r="E110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F110" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J110" s="2" t="inlineStr"/>
-      <c r="K110" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/חטיפים-ושלוקים-קבוצת-מילטין/</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>429 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr"/>
-      <c r="E111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G111" s="5" t="inlineStr">
+      <c r="G96" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -30069,123 +29484,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr">
+      <c r="I96" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J111" s="2" t="inlineStr"/>
-      <c r="K111" s="6" t="inlineStr">
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלקסי</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr"/>
-      <c r="E112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F112" s="2" t="n">
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/טרריומים-קבוצת-מילטין/</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>429 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr"/>
+      <c r="E97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J112" s="2" t="inlineStr"/>
-      <c r="K112" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=בובו-bobo</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr"/>
-      <c r="E113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J113" s="2" t="inlineStr"/>
-      <c r="K113" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/שירותים/</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>429 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr"/>
-      <c r="E114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F114" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G114" s="5" t="inlineStr">
+      <c r="G97" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -30200,84 +29537,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr">
+      <c r="I97" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J114" s="2" t="inlineStr"/>
-      <c r="K114" s="6" t="inlineStr">
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=הביטרייל</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr"/>
-      <c r="E115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F115" s="2" t="n">
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/חולות-קבוצת-מילטין/</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>429 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr"/>
+      <c r="E98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J115" s="2" t="inlineStr"/>
-      <c r="K115" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ab7</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr"/>
-      <c r="E116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G116" s="5" t="inlineStr">
+      <c r="G98" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -30292,84 +29590,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J116" s="2" t="inlineStr"/>
-      <c r="K116" s="6" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ביהפר</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr"/>
-      <c r="E117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F117" s="2" t="n">
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/קולרים-ורצועות/</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>429 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr"/>
+      <c r="E99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I117" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J117" s="2" t="inlineStr"/>
-      <c r="K117" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/טרריומים-קבוצת-מילטין/</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>429 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr"/>
-      <c r="E118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F118" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G118" s="5" t="inlineStr">
+      <c r="G99" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -30384,84 +29643,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J118" s="2" t="inlineStr"/>
-      <c r="K118" s="6" t="inlineStr">
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ספורטדוג</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr"/>
-      <c r="E119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F119" s="2" t="n">
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/משחקים-וצעצועים/</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>429 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr"/>
+      <c r="E100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I119" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J119" s="2" t="inlineStr"/>
-      <c r="K119" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/חולות-קבוצת-מילטין/</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>429 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr"/>
-      <c r="E120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F120" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G120" s="5" t="inlineStr">
+      <c r="G100" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -30476,45 +29696,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I120" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J120" s="2" t="inlineStr"/>
-      <c r="K120" s="6" t="inlineStr">
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=bil-jac</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr"/>
-      <c r="E121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F121" s="2" t="n">
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/kitten-milk-replacers/</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>429 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr"/>
+      <c r="E101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G121" s="5" t="inlineStr">
+      <c r="G101" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -30529,45 +29749,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J121" s="2" t="inlineStr"/>
-      <c r="K121" s="6" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=imac</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr"/>
-      <c r="E122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F122" s="2" t="n">
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/פדים/</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>429 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr"/>
+      <c r="E102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G122" s="5" t="inlineStr">
+      <c r="G102" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -30582,84 +29802,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I122" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J122" s="2" t="inlineStr"/>
-      <c r="K122" s="6" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=וט-לייף-vet-life</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr"/>
-      <c r="E123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F123" s="2" t="n">
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/תכשירי-חינוך/</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>429 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr"/>
+      <c r="E103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J123" s="2" t="inlineStr"/>
-      <c r="K123" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ls</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr"/>
-      <c r="E124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F124" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G124" s="5" t="inlineStr">
+      <c r="G103" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -30674,45 +29855,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J124" s="2" t="inlineStr"/>
-      <c r="K124" s="6" t="inlineStr">
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/קולרים-ורצועות/</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/ציוד-תספורות-קבוצת-מילטין/</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D125" s="2" t="inlineStr"/>
-      <c r="E125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F125" s="2" t="n">
+      <c r="D104" s="2" t="inlineStr"/>
+      <c r="E104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G125" s="5" t="inlineStr">
+      <c r="G104" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -30727,45 +29908,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J125" s="2" t="inlineStr"/>
-      <c r="K125" s="6" t="inlineStr">
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/משחקים-וצעצועים/</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/תיקי-נשיאה/</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D126" s="2" t="inlineStr"/>
-      <c r="E126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F126" s="2" t="n">
+      <c r="D105" s="2" t="inlineStr"/>
+      <c r="E105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G126" s="5" t="inlineStr">
+      <c r="G105" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -30780,84 +29961,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J126" s="2" t="inlineStr"/>
-      <c r="K126" s="6" t="inlineStr">
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=קאנטרי-country</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr"/>
-      <c r="E127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F127" s="2" t="n">
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/תכשירי-חינוך-קבוצת-מילטין/</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>429 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr"/>
+      <c r="E106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J127" s="2" t="inlineStr"/>
-      <c r="K127" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/kitten-milk-replacers/</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>429 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr"/>
-      <c r="E128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G128" s="5" t="inlineStr">
+      <c r="G106" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -30872,123 +30014,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I128" s="2" t="inlineStr">
+      <c r="I106" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J128" s="2" t="inlineStr"/>
-      <c r="K128" s="6" t="inlineStr">
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=דוג-איט</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr"/>
-      <c r="E129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F129" s="2" t="n">
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/מצע/</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>429 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr"/>
+      <c r="E107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I129" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J129" s="2" t="inlineStr"/>
-      <c r="K129" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=מרפי-murphy</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr"/>
-      <c r="E130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F130" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I130" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J130" s="2" t="inlineStr"/>
-      <c r="K130" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/פדים/</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>429 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr"/>
-      <c r="E131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F131" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G131" s="5" t="inlineStr">
+      <c r="G107" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -31003,45 +30067,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J131" s="2" t="inlineStr"/>
-      <c r="K131" s="6" t="inlineStr">
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/תכשירי-חינוך/</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/תוספי-תזונה/</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D132" s="2" t="inlineStr"/>
-      <c r="E132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F132" s="2" t="n">
+      <c r="D108" s="2" t="inlineStr"/>
+      <c r="E108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G132" s="5" t="inlineStr">
+      <c r="G108" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -31056,123 +30120,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I132" s="2" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J132" s="2" t="inlineStr"/>
-      <c r="K132" s="6" t="inlineStr">
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=קומר</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr"/>
-      <c r="E133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F133" s="2" t="n">
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/חטיפים-ושלוקים/</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>429 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr"/>
+      <c r="E109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I133" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J133" s="2" t="inlineStr"/>
-      <c r="K133" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=אנד-אן-די-nd</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr"/>
-      <c r="E134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F134" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I134" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J134" s="2" t="inlineStr"/>
-      <c r="K134" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/ציוד-תספורות-קבוצת-מילטין/</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>429 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr"/>
-      <c r="E135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F135" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G135" s="5" t="inlineStr">
+      <c r="G109" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -31187,45 +30173,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr">
+      <c r="I109" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J135" s="2" t="inlineStr"/>
-      <c r="K135" s="6" t="inlineStr">
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/תיקי-נשיאה/</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/ציוד-תספורות/</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr"/>
-      <c r="E136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F136" s="2" t="n">
+      <c r="D110" s="2" t="inlineStr"/>
+      <c r="E110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G136" s="5" t="inlineStr">
+      <c r="G110" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -31240,84 +30226,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr">
+      <c r="I110" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J136" s="2" t="inlineStr"/>
-      <c r="K136" s="6" t="inlineStr">
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=אהיים-eheim</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr"/>
-      <c r="E137" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F137" s="2" t="n">
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/ציוד-לקולרים-ולרצועות/</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>429 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr"/>
+      <c r="E111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I137" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J137" s="2" t="inlineStr"/>
-      <c r="K137" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/תכשירי-חינוך-קבוצת-מילטין/</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>429 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr"/>
-      <c r="E138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F138" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G138" s="5" t="inlineStr">
+      <c r="G111" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -31332,84 +30279,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr">
+      <c r="I111" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J138" s="2" t="inlineStr"/>
-      <c r="K138" s="6" t="inlineStr">
+      <c r="J111" s="2" t="inlineStr"/>
+      <c r="K111" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=לה-קט-la-cat</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr"/>
-      <c r="E139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F139" s="2" t="n">
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/מזון-טיפולי-קבוצת-מילטין/</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>429 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr"/>
+      <c r="E112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I139" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J139" s="2" t="inlineStr"/>
-      <c r="K139" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/מצע/</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>429 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr"/>
-      <c r="E140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F140" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G140" s="5" t="inlineStr">
+      <c r="G112" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -31424,84 +30332,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr">
+      <c r="I112" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J140" s="2" t="inlineStr"/>
-      <c r="K140" s="6" t="inlineStr">
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גאגל-jajale</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr"/>
-      <c r="E141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F141" s="2" t="n">
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/משאבות-מים-ומזרקות/</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>429 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr"/>
+      <c r="E113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I141" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J141" s="2" t="inlineStr"/>
-      <c r="K141" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=beeztees</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr"/>
-      <c r="E142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F142" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G142" s="5" t="inlineStr">
+      <c r="G113" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -31516,435 +30385,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J142" s="2" t="inlineStr"/>
-      <c r="K142" s="6" t="inlineStr">
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr"/>
+      <c r="K113" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=אקספרט</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr"/>
-      <c r="E143" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F143" s="2" t="n">
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/קולרים/</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>429 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr"/>
+      <c r="E114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I143" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J143" s="2" t="inlineStr"/>
-      <c r="K143" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ציקוס-chicos</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr"/>
-      <c r="E144" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F144" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I144" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J144" s="2" t="inlineStr"/>
-      <c r="K144" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=איי-דוג</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr"/>
-      <c r="E145" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F145" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I145" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J145" s="2" t="inlineStr"/>
-      <c r="K145" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=מרינה</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr"/>
-      <c r="E146" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F146" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I146" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J146" s="2" t="inlineStr"/>
-      <c r="K146" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=טרופיפיט</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr"/>
-      <c r="E147" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F147" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I147" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J147" s="2" t="inlineStr"/>
-      <c r="K147" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=מונג</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr"/>
-      <c r="E148" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F148" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I148" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J148" s="2" t="inlineStr"/>
-      <c r="K148" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פרו-קולין</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr"/>
-      <c r="E149" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F149" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I149" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J149" s="2" t="inlineStr"/>
-      <c r="K149" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=טרופיקל</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr"/>
-      <c r="E150" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F150" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I150" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J150" s="2" t="inlineStr"/>
-      <c r="K150" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=סימבה</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr"/>
-      <c r="E151" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F151" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I151" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J151" s="2" t="inlineStr"/>
-      <c r="K151" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=pro-plan-פרו-פלן</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr"/>
-      <c r="E152" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F152" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I152" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J152" s="2" t="inlineStr"/>
-      <c r="K152" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/תוספי-תזונה/</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>429 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr"/>
-      <c r="E153" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F153" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G153" s="5" t="inlineStr">
+      <c r="G114" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -31959,45 +30438,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I153" s="2" t="inlineStr">
+      <c r="I114" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J153" s="2" t="inlineStr"/>
-      <c r="K153" s="6" t="inlineStr">
+      <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=odog</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr"/>
-      <c r="E154" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F154" s="2" t="n">
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/רתמות/</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>429 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr"/>
+      <c r="E115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G154" s="5" t="inlineStr">
+      <c r="G115" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -32012,123 +30491,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I154" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J154" s="2" t="inlineStr"/>
-      <c r="K154" s="6" t="inlineStr">
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr"/>
+      <c r="K115" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גוסיקט</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr"/>
-      <c r="E155" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F155" s="2" t="n">
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/עצמות/</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>429 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr"/>
+      <c r="E116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I155" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J155" s="2" t="inlineStr"/>
-      <c r="K155" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פנסי-פיסט-fancy-feast</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr"/>
-      <c r="E156" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F156" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I156" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J156" s="2" t="inlineStr"/>
-      <c r="K156" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=friskies</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr"/>
-      <c r="E157" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F157" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G157" s="5" t="inlineStr">
+      <c r="G116" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -32143,45 +30544,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J157" s="2" t="inlineStr"/>
-      <c r="K157" s="6" t="inlineStr">
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr"/>
+      <c r="K116" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/חטיפים-ושלוקים/</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/חטיפים-ועצמות/</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D158" s="2" t="inlineStr"/>
-      <c r="E158" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F158" s="2" t="n">
+      <c r="D117" s="2" t="inlineStr"/>
+      <c r="E117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G158" s="5" t="inlineStr">
+      <c r="G117" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -32196,84 +30597,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I158" s="2" t="inlineStr">
+      <c r="I117" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J158" s="2" t="inlineStr"/>
-      <c r="K158" s="6" t="inlineStr">
+      <c r="J117" s="2" t="inlineStr"/>
+      <c r="K117" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פטמייט</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr"/>
-      <c r="E159" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F159" s="2" t="n">
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/מברשות-ומסרקים/</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>429 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr"/>
+      <c r="E118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I159" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J159" s="2" t="inlineStr"/>
-      <c r="K159" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/ציוד-תספורות/</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>429 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr"/>
-      <c r="E160" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F160" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G160" s="5" t="inlineStr">
+      <c r="G118" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -32288,162 +30650,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I160" s="2" t="inlineStr">
+      <c r="I118" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J160" s="2" t="inlineStr"/>
-      <c r="K160" s="6" t="inlineStr">
+      <c r="J118" s="2" t="inlineStr"/>
+      <c r="K118" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=וט-סולושיין</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr"/>
-      <c r="E161" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F161" s="2" t="n">
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/שירותים-קבוצת-מילטין/</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>429 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr"/>
+      <c r="E119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I161" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J161" s="2" t="inlineStr"/>
-      <c r="K161" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=אוריגן-orijen</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr"/>
-      <c r="E162" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F162" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I162" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J162" s="2" t="inlineStr"/>
-      <c r="K162" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=שונרא</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr"/>
-      <c r="E163" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F163" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I163" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J163" s="2" t="inlineStr"/>
-      <c r="K163" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/ציוד-לקולרים-ולרצועות/</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>429 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr"/>
-      <c r="E164" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F164" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G164" s="5" t="inlineStr">
+      <c r="G119" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -32458,45 +30703,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I164" s="2" t="inlineStr">
+      <c r="I119" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J164" s="2" t="inlineStr"/>
-      <c r="K164" s="6" t="inlineStr">
+      <c r="J119" s="2" t="inlineStr"/>
+      <c r="K119" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ht</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr"/>
-      <c r="E165" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F165" s="2" t="n">
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/חטיפים-ספקים-חיצוניים/</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>429 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr"/>
+      <c r="E120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G165" s="5" t="inlineStr">
+      <c r="G120" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -32511,45 +30756,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I165" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J165" s="2" t="inlineStr"/>
-      <c r="K165" s="6" t="inlineStr">
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr"/>
+      <c r="K120" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/מזון-טיפולי-קבוצת-מילטין/</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/היגיינת-הפה-קבוצת-מילטין/</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D166" s="2" t="inlineStr"/>
-      <c r="E166" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F166" s="2" t="n">
+      <c r="D121" s="2" t="inlineStr"/>
+      <c r="E121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G166" s="5" t="inlineStr">
+      <c r="G121" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -32564,123 +30809,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I166" s="2" t="inlineStr">
+      <c r="I121" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J166" s="2" t="inlineStr"/>
-      <c r="K166" s="6" t="inlineStr">
+      <c r="J121" s="2" t="inlineStr"/>
+      <c r="K121" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פרוטי</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr"/>
-      <c r="E167" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F167" s="2" t="n">
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/מיטות-ומזרנים-ספקים-חיצוניים/</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>429 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr"/>
+      <c r="E122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I167" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J167" s="2" t="inlineStr"/>
-      <c r="K167" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=קוקו-chicos</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr"/>
-      <c r="E168" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F168" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I168" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J168" s="2" t="inlineStr"/>
-      <c r="K168" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/משאבות-מים-ומזרקות/</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>429 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr"/>
-      <c r="E169" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F169" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G169" s="5" t="inlineStr">
+      <c r="G122" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -32695,84 +30862,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I169" s="2" t="inlineStr">
+      <c r="I122" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J169" s="2" t="inlineStr"/>
-      <c r="K169" s="6" t="inlineStr">
+      <c r="J122" s="2" t="inlineStr"/>
+      <c r="K122" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פרונטליין</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr"/>
-      <c r="E170" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F170" s="2" t="n">
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/product-category/קולרים-ורצועות-חינוך-ספקים-חיצוניים/</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>429 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr"/>
+      <c r="E123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I170" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J170" s="2" t="inlineStr"/>
-      <c r="K170" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/קולרים/</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>429 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr"/>
-      <c r="E171" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F171" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G171" s="5" t="inlineStr">
+      <c r="G123" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
 https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
@@ -32787,1549 +30915,133 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I171" s="2" t="inlineStr">
+      <c r="I123" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J171" s="2" t="inlineStr"/>
-      <c r="K171" s="6" t="inlineStr">
+      <c r="J123" s="2" t="inlineStr"/>
+      <c r="K123" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=אדוונס-advance</t>
-        </is>
-      </c>
-      <c r="B172" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr"/>
-      <c r="E172" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F172" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I172" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J172" s="2" t="inlineStr"/>
-      <c r="K172" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/רתמות/</t>
-        </is>
-      </c>
-      <c r="B173" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>https://zoolu.co.il/persian-cat/</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D173" s="2" t="inlineStr"/>
-      <c r="E173" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F173" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G173" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=דוגטרא-dogtra
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=איי-קט
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ספיקט
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=סוויט-פט-sweet-pet
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=help
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=טרופיקלין
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פטסלנד
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ליוינג-וורלד
-(ועוד 40)</t>
-        </is>
-      </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="inlineStr">
-        <is>
-          <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="inlineStr"/>
-      <c r="K173" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=הילס-hills</t>
-        </is>
-      </c>
-      <c r="B174" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr"/>
-      <c r="E174" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F174" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I174" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J174" s="2" t="inlineStr"/>
-      <c r="K174" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/עצמות/</t>
-        </is>
-      </c>
-      <c r="B175" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>429 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr"/>
-      <c r="E175" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F175" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G175" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=דוגטרא-dogtra
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=איי-קט
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ספיקט
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=סוויט-פט-sweet-pet
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=help
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=טרופיקלין
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פטסלנד
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ליוינג-וורלד
-(ועוד 40)</t>
-        </is>
-      </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="inlineStr">
-        <is>
-          <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="inlineStr"/>
-      <c r="K175" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/חטיפים-ועצמות/</t>
-        </is>
-      </c>
-      <c r="B176" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>429 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr"/>
-      <c r="E176" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F176" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G176" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=דוגטרא-dogtra
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=איי-קט
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ספיקט
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=סוויט-פט-sweet-pet
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=help
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=טרופיקלין
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פטסלנד
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ליוינג-וורלד
-(ועוד 40)</t>
-        </is>
-      </c>
-      <c r="H176" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I176" s="2" t="inlineStr">
-        <is>
-          <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
-        </is>
-      </c>
-      <c r="J176" s="2" t="inlineStr"/>
-      <c r="K176" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=טייסט-אוף-דה-ויילד-taste-of-the-wild</t>
-        </is>
-      </c>
-      <c r="B177" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr"/>
-      <c r="E177" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F177" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I177" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J177" s="2" t="inlineStr"/>
-      <c r="K177" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/מברשות-ומסרקים/</t>
-        </is>
-      </c>
-      <c r="B178" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>429 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr"/>
-      <c r="E178" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F178" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G178" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=דוגטרא-dogtra
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=איי-קט
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ספיקט
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=סוויט-פט-sweet-pet
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=help
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=טרופיקלין
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פטסלנד
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ליוינג-וורלד
-(ועוד 40)</t>
-        </is>
-      </c>
-      <c r="H178" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I178" s="2" t="inlineStr">
-        <is>
-          <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
-        </is>
-      </c>
-      <c r="J178" s="2" t="inlineStr"/>
-      <c r="K178" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/שירותים-קבוצת-מילטין/</t>
-        </is>
-      </c>
-      <c r="B179" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>429 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr"/>
-      <c r="E179" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F179" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G179" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=דוגטרא-dogtra
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=איי-קט
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ספיקט
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=סוויט-פט-sweet-pet
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=help
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=טרופיקלין
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פטסלנד
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ליוינג-וורלד
-(ועוד 40)</t>
-        </is>
-      </c>
-      <c r="H179" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I179" s="2" t="inlineStr">
-        <is>
-          <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
-        </is>
-      </c>
-      <c r="J179" s="2" t="inlineStr"/>
-      <c r="K179" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=קונג</t>
-        </is>
-      </c>
-      <c r="B180" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr"/>
-      <c r="E180" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F180" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I180" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J180" s="2" t="inlineStr"/>
-      <c r="K180" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=מולטיפט-multipet</t>
-        </is>
-      </c>
-      <c r="B181" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr"/>
-      <c r="E181" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F181" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I181" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J181" s="2" t="inlineStr"/>
-      <c r="K181" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=מימיקט</t>
-        </is>
-      </c>
-      <c r="B182" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr"/>
-      <c r="E182" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F182" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I182" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J182" s="2" t="inlineStr"/>
-      <c r="K182" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=נוטרפין</t>
-        </is>
-      </c>
-      <c r="B183" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr"/>
-      <c r="E183" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F183" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G183" s="2" t="inlineStr"/>
-      <c r="H183" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I183" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J183" s="2" t="inlineStr"/>
-      <c r="K183" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=קונפיס</t>
-        </is>
-      </c>
-      <c r="B184" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr"/>
-      <c r="E184" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F184" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G184" s="2" t="inlineStr"/>
-      <c r="H184" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I184" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J184" s="2" t="inlineStr"/>
-      <c r="K184" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=מותגים-אחרים</t>
-        </is>
-      </c>
-      <c r="B185" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr"/>
-      <c r="E185" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F185" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G185" s="2" t="inlineStr"/>
-      <c r="H185" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I185" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J185" s="2" t="inlineStr"/>
-      <c r="K185" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=שיבא</t>
-        </is>
-      </c>
-      <c r="B186" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr"/>
-      <c r="E186" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F186" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G186" s="2" t="inlineStr"/>
-      <c r="H186" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I186" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J186" s="2" t="inlineStr"/>
-      <c r="K186" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=להשאט</t>
-        </is>
-      </c>
-      <c r="B187" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C187" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D187" s="2" t="inlineStr"/>
-      <c r="E187" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F187" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G187" s="2" t="inlineStr"/>
-      <c r="H187" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I187" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J187" s="2" t="inlineStr"/>
-      <c r="K187" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/חטיפים-ספקים-חיצוניים/</t>
-        </is>
-      </c>
-      <c r="B188" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>429 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="inlineStr"/>
-      <c r="E188" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F188" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G188" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=דוגטרא-dogtra
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=איי-קט
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ספיקט
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=סוויט-פט-sweet-pet
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=help
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=טרופיקלין
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פטסלנד
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ליוינג-וורלד
-(ועוד 40)</t>
-        </is>
-      </c>
-      <c r="H188" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I188" s="2" t="inlineStr">
-        <is>
-          <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
-        </is>
-      </c>
-      <c r="J188" s="2" t="inlineStr"/>
-      <c r="K188" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=afp</t>
-        </is>
-      </c>
-      <c r="B189" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C189" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D189" s="2" t="inlineStr"/>
-      <c r="E189" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F189" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G189" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=דוגטרא-dogtra
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=איי-קט
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ספיקט
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=סוויט-פט-sweet-pet
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=help
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=טרופיקלין
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פטסלנד
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ליוינג-וורלד
-(ועוד 40)</t>
-        </is>
-      </c>
-      <c r="H189" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I189" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J189" s="2" t="inlineStr"/>
-      <c r="K189" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=marley-and-me</t>
-        </is>
-      </c>
-      <c r="B190" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D190" s="2" t="inlineStr"/>
-      <c r="E190" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F190" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G190" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=דוגטרא-dogtra
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=איי-קט
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ספיקט
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=סוויט-פט-sweet-pet
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=help
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=טרופיקלין
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פטסלנד
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ליוינג-וורלד
-(ועוד 40)</t>
-        </is>
-      </c>
-      <c r="H190" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I190" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J190" s="2" t="inlineStr"/>
-      <c r="K190" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=סיזר</t>
-        </is>
-      </c>
-      <c r="B191" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D191" s="2" t="inlineStr"/>
-      <c r="E191" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F191" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G191" s="2" t="inlineStr"/>
-      <c r="H191" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I191" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J191" s="2" t="inlineStr"/>
-      <c r="K191" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ocat</t>
-        </is>
-      </c>
-      <c r="B192" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="inlineStr"/>
-      <c r="E192" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F192" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G192" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=דוגטרא-dogtra
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=איי-קט
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ספיקט
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=סוויט-פט-sweet-pet
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=help
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=טרופיקלין
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פטסלנד
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ליוינג-וורלד
-(ועוד 40)</t>
-        </is>
-      </c>
-      <c r="H192" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I192" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J192" s="2" t="inlineStr"/>
-      <c r="K192" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ויבוקס</t>
-        </is>
-      </c>
-      <c r="B193" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D193" s="2" t="inlineStr"/>
-      <c r="E193" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F193" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G193" s="2" t="inlineStr"/>
-      <c r="H193" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I193" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J193" s="2" t="inlineStr"/>
-      <c r="K193" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פיש-פרנד</t>
-        </is>
-      </c>
-      <c r="B194" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="inlineStr"/>
-      <c r="E194" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F194" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G194" s="2" t="inlineStr"/>
-      <c r="H194" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I194" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J194" s="2" t="inlineStr"/>
-      <c r="K194" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ויסקאס</t>
-        </is>
-      </c>
-      <c r="B195" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="inlineStr"/>
-      <c r="E195" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F195" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G195" s="2" t="inlineStr"/>
-      <c r="H195" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I195" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J195" s="2" t="inlineStr"/>
-      <c r="K195" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/היגיינת-הפה-קבוצת-מילטין/</t>
-        </is>
-      </c>
-      <c r="B196" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>429 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D196" s="2" t="inlineStr"/>
-      <c r="E196" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F196" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G196" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=דוגטרא-dogtra
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=איי-קט
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ספיקט
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=סוויט-פט-sweet-pet
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=help
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=טרופיקלין
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פטסלנד
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ליוינג-וורלד
-(ועוד 40)</t>
-        </is>
-      </c>
-      <c r="H196" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I196" s="2" t="inlineStr">
-        <is>
-          <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
-        </is>
-      </c>
-      <c r="J196" s="2" t="inlineStr"/>
-      <c r="K196" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=וולנס-קור</t>
-        </is>
-      </c>
-      <c r="B197" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D197" s="2" t="inlineStr"/>
-      <c r="E197" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F197" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G197" s="2" t="inlineStr"/>
-      <c r="H197" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I197" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J197" s="2" t="inlineStr"/>
-      <c r="K197" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=רויאל-קנין-royal-canin</t>
-        </is>
-      </c>
-      <c r="B198" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="inlineStr"/>
-      <c r="E198" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F198" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G198" s="2" t="inlineStr"/>
-      <c r="H198" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I198" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J198" s="2" t="inlineStr"/>
-      <c r="K198" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=באווארו</t>
-        </is>
-      </c>
-      <c r="B199" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C199" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D199" s="2" t="inlineStr"/>
-      <c r="E199" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F199" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G199" s="2" t="inlineStr"/>
-      <c r="H199" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I199" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J199" s="2" t="inlineStr"/>
-      <c r="K199" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/מיטות-ומזרנים-ספקים-חיצוניים/</t>
-        </is>
-      </c>
-      <c r="B200" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C200" s="2" t="inlineStr">
-        <is>
-          <t>429 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D200" s="2" t="inlineStr"/>
-      <c r="E200" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F200" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G200" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=דוגטרא-dogtra
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=איי-קט
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ספיקט
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=סוויט-פט-sweet-pet
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=help
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=טרופיקלין
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פטסלנד
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ליוינג-וורלד
-(ועוד 40)</t>
-        </is>
-      </c>
-      <c r="H200" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I200" s="2" t="inlineStr">
-        <is>
-          <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
-        </is>
-      </c>
-      <c r="J200" s="2" t="inlineStr"/>
-      <c r="K200" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלאק-אוף</t>
-        </is>
-      </c>
-      <c r="B201" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C201" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D201" s="2" t="inlineStr"/>
-      <c r="E201" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F201" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G201" s="2" t="inlineStr"/>
-      <c r="H201" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I201" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J201" s="2" t="inlineStr"/>
-      <c r="K201" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/product-category/קולרים-ורצועות-חינוך-ספקים-חיצוניים/</t>
-        </is>
-      </c>
-      <c r="B202" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>429 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D202" s="2" t="inlineStr"/>
-      <c r="E202" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F202" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G202" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פלוטו
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=גטולינו
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=דוגטרא-dogtra
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=איי-קט
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ספיקט
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=סוויט-פט-sweet-pet
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=help
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=טרופיקלין
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=פטסלנד
-https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ליוינג-וורלד
-(ועוד 40)</t>
-        </is>
-      </c>
-      <c r="H202" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I202" s="2" t="inlineStr">
-        <is>
-          <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
-        </is>
-      </c>
-      <c r="J202" s="2" t="inlineStr"/>
-      <c r="K202" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/food-brands/גוסרה/?nf_brands=ויטה-מולן</t>
-        </is>
-      </c>
-      <c r="B203" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק</t>
-        </is>
-      </c>
-      <c r="D203" s="2" t="inlineStr"/>
-      <c r="E203" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F203" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G203" s="2" t="inlineStr"/>
-      <c r="H203" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I203" s="2" t="inlineStr">
-        <is>
-          <t>לא נבדק שוב בנפרד; כתובות מאותה משפחת כתובות שנבדקו ב-27.09.2026 החזירו 200. הקוד בסריקה נובע מהגבלת קצב לסורק.</t>
-        </is>
-      </c>
-      <c r="J203" s="2" t="inlineStr"/>
-      <c r="K203" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="5" t="inlineStr">
-        <is>
-          <t>https://zoolu.co.il/persian-cat/</t>
-        </is>
-      </c>
-      <c r="B204" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>429 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D204" s="2" t="inlineStr"/>
-      <c r="E204" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F204" s="2" t="n">
+      <c r="D124" s="2" t="inlineStr"/>
+      <c r="E124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G204" s="5" t="inlineStr">
+      <c r="G124" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/persian-cat/
 https://zoolu.co.il/?utm_source=chatgpt.com</t>
         </is>
       </c>
-      <c r="H204" s="2" t="inlineStr">
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I204" s="2" t="inlineStr">
+      <c r="I124" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J204" s="2" t="inlineStr"/>
-      <c r="K204" s="6" t="inlineStr">
+      <c r="J124" s="2" t="inlineStr"/>
+      <c r="K124" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="5" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/summer-safety-tips-for-dogs1/</t>
         </is>
       </c>
-      <c r="B205" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C205" s="2" t="inlineStr">
+      <c r="B125" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D205" s="2" t="inlineStr"/>
-      <c r="E205" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F205" s="2" t="n">
+      <c r="D125" s="2" t="inlineStr"/>
+      <c r="E125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G205" s="5" t="inlineStr">
+      <c r="G125" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/summer-safety-tips-for-dogs1/
 https://zoolu.co.il/?utm_source=chatgpt.com</t>
         </is>
       </c>
-      <c r="H205" s="2" t="inlineStr">
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I205" s="2" t="inlineStr">
+      <c r="I125" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J205" s="2" t="inlineStr"/>
-      <c r="K205" s="6" t="inlineStr">
+      <c r="J125" s="2" t="inlineStr"/>
+      <c r="K125" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="5" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/אימאק-בית-מסתור-לאוגר/</t>
         </is>
       </c>
-      <c r="B206" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
+      <c r="B126" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D206" s="2" t="inlineStr"/>
-      <c r="E206" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F206" s="2" t="n">
+      <c r="D126" s="2" t="inlineStr"/>
+      <c r="E126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G206" s="5" t="inlineStr">
+      <c r="G126" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/אימאק-גלגל-כושר-לאוגרים/
 https://zoolu.co.il/product/הביטרייל-כלוב-לאוגרים-דגם-ריטריט/
@@ -34341,45 +31053,45 @@
 https://zoolu.co.il/product-category/דקורציה-קבוצת-מילטין/</t>
         </is>
       </c>
-      <c r="H206" s="2" t="inlineStr">
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I206" s="2" t="inlineStr">
+      <c r="I126" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J206" s="2" t="inlineStr"/>
-      <c r="K206" s="6" t="inlineStr">
+      <c r="J126" s="2" t="inlineStr"/>
+      <c r="K126" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="5" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/ליווינג-וורלד-גלגלת-אימון-לאוגרים-14ס/</t>
         </is>
       </c>
-      <c r="B207" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C207" s="2" t="inlineStr">
+      <c r="B127" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D207" s="2" t="inlineStr"/>
-      <c r="E207" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F207" s="2" t="n">
+      <c r="D127" s="2" t="inlineStr"/>
+      <c r="E127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G207" s="5" t="inlineStr">
+      <c r="G127" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/אימאק-גלגל-כושר-לאוגרים/
 https://zoolu.co.il/product/אימאק-כלוב-פנטזיה-לאוגר/
@@ -34387,45 +31099,45 @@
 https://zoolu.co.il/product-category/דקורציה-קבוצת-מילטין/</t>
         </is>
       </c>
-      <c r="H207" s="2" t="inlineStr">
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I207" s="2" t="inlineStr">
+      <c r="I127" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J207" s="2" t="inlineStr"/>
-      <c r="K207" s="6" t="inlineStr">
+      <c r="J127" s="2" t="inlineStr"/>
+      <c r="K127" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="5" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/אימאק-גלגל-כושר-לאוגרים/</t>
         </is>
       </c>
-      <c r="B208" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C208" s="2" t="inlineStr">
+      <c r="B128" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D208" s="2" t="inlineStr"/>
-      <c r="E208" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F208" s="2" t="n">
+      <c r="D128" s="2" t="inlineStr"/>
+      <c r="E128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G208" s="5" t="inlineStr">
+      <c r="G128" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/אימאק-גלגל-כושר-לאוגרים/
 https://zoolu.co.il/product/אימאק-מתקן-שתייה-ביבר-300-למכרסמים/
@@ -34434,89 +31146,89 @@
 https://zoolu.co.il/product-category/דקורציה-קבוצת-מילטין/</t>
         </is>
       </c>
-      <c r="H208" s="2" t="inlineStr">
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I208" s="2" t="inlineStr">
+      <c r="I128" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J208" s="2" t="inlineStr"/>
-      <c r="K208" s="6" t="inlineStr">
+      <c r="J128" s="2" t="inlineStr"/>
+      <c r="K128" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="5" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/jbl-מצע-לצמחיה-3-ליטר/</t>
         </is>
       </c>
-      <c r="B209" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C209" s="2" t="inlineStr">
+      <c r="B129" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D209" s="2" t="inlineStr"/>
-      <c r="E209" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F209" s="2" t="n">
+      <c r="D129" s="2" t="inlineStr"/>
+      <c r="E129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G209" s="5" t="inlineStr">
+      <c r="G129" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/jbl-מצע-לצמחיה-3-ליטר/
 https://zoolu.co.il/product-category/דקורציה/?nf_brands=גי-בי-אל-jbl</t>
         </is>
       </c>
-      <c r="H209" s="2" t="inlineStr">
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I209" s="2" t="inlineStr">
+      <c r="I129" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J209" s="2" t="inlineStr"/>
-      <c r="K209" s="6" t="inlineStr">
+      <c r="J129" s="2" t="inlineStr"/>
+      <c r="K129" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="5" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/אימאק-כלוב-בני-100-למכרסמים/</t>
         </is>
       </c>
-      <c r="B210" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C210" s="2" t="inlineStr">
+      <c r="B130" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D210" s="2" t="inlineStr"/>
-      <c r="E210" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F210" s="2" t="n">
+      <c r="D130" s="2" t="inlineStr"/>
+      <c r="E130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G210" s="5" t="inlineStr">
+      <c r="G130" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/אימאק-כלוב-בני-100-למכרסמים/
 https://zoolu.co.il/product/אימאק-כלוב-קריסטי-2-לאוגר/
@@ -34524,131 +31236,131 @@
 https://zoolu.co.il/product-category/כלובים-קבוצת-מילטין/</t>
         </is>
       </c>
-      <c r="H210" s="2" t="inlineStr">
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I210" s="2" t="inlineStr">
+      <c r="I130" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J210" s="2" t="inlineStr"/>
-      <c r="K210" s="6" t="inlineStr">
+      <c r="J130" s="2" t="inlineStr"/>
+      <c r="K130" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="5" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/אימאק-כלוב-איזי-80-למכרסמים/</t>
         </is>
       </c>
-      <c r="B211" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C211" s="2" t="inlineStr">
+      <c r="B131" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D211" s="2" t="inlineStr"/>
-      <c r="E211" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F211" s="2" t="n">
+      <c r="D131" s="2" t="inlineStr"/>
+      <c r="E131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G211" s="5" t="inlineStr">
+      <c r="G131" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/כלובים-קבוצת-מילטין/</t>
         </is>
       </c>
-      <c r="H211" s="2" t="inlineStr">
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I211" s="2" t="inlineStr">
+      <c r="I131" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J211" s="2" t="inlineStr"/>
-      <c r="K211" s="6" t="inlineStr">
+      <c r="J131" s="2" t="inlineStr"/>
+      <c r="K131" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="5" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/איאמק-כלוב-רוני-80-למכרסמים/</t>
         </is>
       </c>
-      <c r="B212" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C212" s="2" t="inlineStr">
+      <c r="B132" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D212" s="2" t="inlineStr"/>
-      <c r="E212" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F212" s="2" t="n">
+      <c r="D132" s="2" t="inlineStr"/>
+      <c r="E132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G212" s="5" t="inlineStr">
+      <c r="G132" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/כלובים-קבוצת-מילטין/</t>
         </is>
       </c>
-      <c r="H212" s="2" t="inlineStr">
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I212" s="2" t="inlineStr">
+      <c r="I132" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J212" s="2" t="inlineStr"/>
-      <c r="K212" s="6" t="inlineStr">
+      <c r="J132" s="2" t="inlineStr"/>
+      <c r="K132" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="5" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/אימאק-כלוב-קריסטי-9-לאוגר/</t>
         </is>
       </c>
-      <c r="B213" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C213" s="2" t="inlineStr">
+      <c r="B133" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D213" s="2" t="inlineStr"/>
-      <c r="E213" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F213" s="2" t="n">
+      <c r="D133" s="2" t="inlineStr"/>
+      <c r="E133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G213" s="5" t="inlineStr">
+      <c r="G133" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/הביטרייל-כלוב-לאוגרים-דגם-ריטריט/
 https://zoolu.co.il/product/אימאק-כלוב-בני-100-למכרסמים/
@@ -34658,45 +31370,45 @@
 https://zoolu.co.il/product-category/כלובים-קבוצת-מילטין/</t>
         </is>
       </c>
-      <c r="H213" s="2" t="inlineStr">
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I213" s="2" t="inlineStr">
+      <c r="I133" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J213" s="2" t="inlineStr"/>
-      <c r="K213" s="6" t="inlineStr">
+      <c r="J133" s="2" t="inlineStr"/>
+      <c r="K133" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="5" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/אימאק-כלוב-רוני-100-למכרסמים/</t>
         </is>
       </c>
-      <c r="B214" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C214" s="2" t="inlineStr">
+      <c r="B134" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D214" s="2" t="inlineStr"/>
-      <c r="E214" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F214" s="2" t="n">
+      <c r="D134" s="2" t="inlineStr"/>
+      <c r="E134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G214" s="5" t="inlineStr">
+      <c r="G134" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/הביטרייל-כלוב-לאוגרים-דגם-ריטריט/
 https://zoolu.co.il/product/אימאק-כלוב-בני-100-למכרסמים/
@@ -34706,45 +31418,45 @@
 https://zoolu.co.il/product-category/כלובים-קבוצת-מילטין/</t>
         </is>
       </c>
-      <c r="H214" s="2" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I214" s="2" t="inlineStr">
+      <c r="I134" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J214" s="2" t="inlineStr"/>
-      <c r="K214" s="6" t="inlineStr">
+      <c r="J134" s="2" t="inlineStr"/>
+      <c r="K134" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="5" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/אימאק-כלוב-שקוף-יויו-פלוס-לאוגר/</t>
         </is>
       </c>
-      <c r="B215" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C215" s="2" t="inlineStr">
+      <c r="B135" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D215" s="2" t="inlineStr"/>
-      <c r="E215" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F215" s="2" t="n">
+      <c r="D135" s="2" t="inlineStr"/>
+      <c r="E135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G215" s="5" t="inlineStr">
+      <c r="G135" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/הביטרייל-כלוב-לאוגרים-דגם-ריטריט/
 https://zoolu.co.il/product/אימאק-כלוב-בני-100-למכרסמים/
@@ -34754,731 +31466,731 @@
 https://zoolu.co.il/product-category/כלובים-קבוצת-מילטין/</t>
         </is>
       </c>
-      <c r="H215" s="2" t="inlineStr">
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I215" s="2" t="inlineStr">
+      <c r="I135" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J215" s="2" t="inlineStr"/>
-      <c r="K215" s="6" t="inlineStr">
+      <c r="J135" s="2" t="inlineStr"/>
+      <c r="K135" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="5" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/jbl-רשת-דגים-פרמיום-שחורה-לבחירה-ב-4-גדלים-ש/</t>
         </is>
       </c>
-      <c r="B216" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C216" s="2" t="inlineStr">
+      <c r="B136" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D216" s="2" t="inlineStr"/>
-      <c r="E216" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F216" s="2" t="n">
+      <c r="D136" s="2" t="inlineStr"/>
+      <c r="E136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G216" s="5" t="inlineStr">
+      <c r="G136" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/אקווטיקה/accessories/
 https://zoolu.co.il/product-category/אבני-אוויר-קבוצת-מילטין/</t>
         </is>
       </c>
-      <c r="H216" s="2" t="inlineStr">
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I216" s="2" t="inlineStr">
+      <c r="I136" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J216" s="2" t="inlineStr"/>
-      <c r="K216" s="6" t="inlineStr">
+      <c r="J136" s="2" t="inlineStr"/>
+      <c r="K136" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="5" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/טרופיקלין-מי-פה-לחתול-בשני-גדלים-לבחיר/</t>
         </is>
       </c>
-      <c r="B217" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C217" s="2" t="inlineStr">
+      <c r="B137" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D217" s="2" t="inlineStr"/>
-      <c r="E217" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F217" s="2" t="n">
+      <c r="D137" s="2" t="inlineStr"/>
+      <c r="E137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G217" s="5" t="inlineStr">
+      <c r="G137" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/cats/cat-grooming-products/
 https://zoolu.co.il/product-category/טיפוח/
 https://zoolu.co.il/product-category/היגיינת-הפה-קבוצת-מילטין/</t>
         </is>
       </c>
-      <c r="H217" s="2" t="inlineStr">
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I217" s="2" t="inlineStr">
+      <c r="I137" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J217" s="2" t="inlineStr"/>
-      <c r="K217" s="6" t="inlineStr">
+      <c r="J137" s="2" t="inlineStr"/>
+      <c r="K137" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="5" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/ליווינג-וורלד-מנהרה-צבעונית-למכרסמים/</t>
         </is>
       </c>
-      <c r="B218" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C218" s="2" t="inlineStr">
+      <c r="B138" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D218" s="2" t="inlineStr"/>
-      <c r="E218" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F218" s="2" t="n">
+      <c r="D138" s="2" t="inlineStr"/>
+      <c r="E138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G218" s="5" t="inlineStr">
+      <c r="G138" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/צעצועים/
 https://zoolu.co.il/product-category/צעצועים-קבוצת-מילטין/</t>
         </is>
       </c>
-      <c r="H218" s="2" t="inlineStr">
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I218" s="2" t="inlineStr">
+      <c r="I138" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J218" s="2" t="inlineStr"/>
-      <c r="K218" s="6" t="inlineStr">
+      <c r="J138" s="2" t="inlineStr"/>
+      <c r="K138" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="5" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/ליווינג-וורלד-בקתת-עץ-למכרסמים/</t>
         </is>
       </c>
-      <c r="B219" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C219" s="2" t="inlineStr">
+      <c r="B139" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D219" s="2" t="inlineStr"/>
-      <c r="E219" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F219" s="2" t="n">
+      <c r="D139" s="2" t="inlineStr"/>
+      <c r="E139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G219" s="5" t="inlineStr">
+      <c r="G139" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/ליווינג-וורלד-בקתת-עץ-למכרסמים/
 https://zoolu.co.il/product-category/צעצועים/
 https://zoolu.co.il/product-category/צעצועים-קבוצת-מילטין/</t>
         </is>
       </c>
-      <c r="H219" s="2" t="inlineStr">
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I219" s="2" t="inlineStr">
+      <c r="I139" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J219" s="2" t="inlineStr"/>
-      <c r="K219" s="6" t="inlineStr">
+      <c r="J139" s="2" t="inlineStr"/>
+      <c r="K139" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="5" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/ליווינג-וורלד-שירותים-פינתיים-למכרסמ/</t>
         </is>
       </c>
-      <c r="B220" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C220" s="2" t="inlineStr">
+      <c r="B140" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D220" s="2" t="inlineStr"/>
-      <c r="E220" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F220" s="2" t="n">
+      <c r="D140" s="2" t="inlineStr"/>
+      <c r="E140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G220" s="2" t="inlineStr"/>
-      <c r="H220" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I220" s="2" t="inlineStr">
+      <c r="I140" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J220" s="2" t="inlineStr"/>
-      <c r="K220" s="6" t="inlineStr">
+      <c r="J140" s="2" t="inlineStr"/>
+      <c r="K140" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="5" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/ביהפר-ויטו-אמפולות-נגד-פרעושים-לכלב/</t>
         </is>
       </c>
-      <c r="B221" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C221" s="2" t="inlineStr">
+      <c r="B141" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D221" s="2" t="inlineStr"/>
-      <c r="E221" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F221" s="2" t="n">
+      <c r="D141" s="2" t="inlineStr"/>
+      <c r="E141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G221" s="5" t="inlineStr">
+      <c r="G141" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/הדברה-קבוצת-מילטין/</t>
         </is>
       </c>
-      <c r="H221" s="2" t="inlineStr">
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I221" s="2" t="inlineStr">
+      <c r="I141" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J221" s="2" t="inlineStr"/>
-      <c r="K221" s="6" t="inlineStr">
+      <c r="J141" s="2" t="inlineStr"/>
+      <c r="K141" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="5" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/ab7-אבקת-פרעושים-לכלב-חתול-150-גר/</t>
         </is>
       </c>
-      <c r="B222" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C222" s="2" t="inlineStr">
+      <c r="B142" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D222" s="2" t="inlineStr"/>
-      <c r="E222" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F222" s="2" t="n">
+      <c r="D142" s="2" t="inlineStr"/>
+      <c r="E142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G222" s="5" t="inlineStr">
+      <c r="G142" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/ab7-אבקת-פרעושים-לכלב-חתול-150-גר/
 https://zoolu.co.il/product-category/הדברה-קבוצת-מילטין/</t>
         </is>
       </c>
-      <c r="H222" s="2" t="inlineStr">
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I222" s="2" t="inlineStr">
+      <c r="I142" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J222" s="2" t="inlineStr"/>
-      <c r="K222" s="6" t="inlineStr">
+      <c r="J142" s="2" t="inlineStr"/>
+      <c r="K142" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="5" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/פרונטליין-טריאקט-אמפולות-לכלבים-מגזע/</t>
         </is>
       </c>
-      <c r="B223" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C223" s="2" t="inlineStr">
+      <c r="B143" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D223" s="2" t="inlineStr"/>
-      <c r="E223" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F223" s="2" t="n">
+      <c r="D143" s="2" t="inlineStr"/>
+      <c r="E143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G223" s="5" t="inlineStr">
+      <c r="G143" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/פרונטליין-טריאקט-אמפולות-לכלבים-מגזע/
 https://zoolu.co.il/product-category/הדברה-קבוצת-מילטין/</t>
         </is>
       </c>
-      <c r="H223" s="2" t="inlineStr">
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I223" s="2" t="inlineStr">
+      <c r="I143" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J223" s="2" t="inlineStr"/>
-      <c r="K223" s="6" t="inlineStr">
+      <c r="J143" s="2" t="inlineStr"/>
+      <c r="K143" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="5" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/גוסרה-הלפ-מזון-טיפולי-רנאל-לחתולים/</t>
         </is>
       </c>
-      <c r="B224" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C224" s="2" t="inlineStr">
+      <c r="B144" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D224" s="2" t="inlineStr"/>
-      <c r="E224" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F224" s="2" t="n">
+      <c r="D144" s="2" t="inlineStr"/>
+      <c r="E144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G224" s="5" t="inlineStr">
+      <c r="G144" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/גוסרה-הלפ-מזון-טיפולי-רנאל-לחתולים/</t>
         </is>
       </c>
-      <c r="H224" s="2" t="inlineStr">
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I224" s="2" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J224" s="2" t="inlineStr"/>
-      <c r="K224" s="6" t="inlineStr">
+      <c r="J144" s="2" t="inlineStr"/>
+      <c r="K144" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="5" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/גוסרה-מזון-יבש-לחתולים-ות-מסורסים-מעו/</t>
         </is>
       </c>
-      <c r="B225" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C225" s="2" t="inlineStr">
+      <c r="B145" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D225" s="2" t="inlineStr"/>
-      <c r="E225" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F225" s="2" t="n">
+      <c r="D145" s="2" t="inlineStr"/>
+      <c r="E145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G225" s="5" t="inlineStr">
+      <c r="G145" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/גוסרה-מזון-יבש-לחתולים-ות-מסורסים-מעו/</t>
         </is>
       </c>
-      <c r="H225" s="2" t="inlineStr">
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I225" s="2" t="inlineStr">
+      <c r="I145" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J225" s="2" t="inlineStr"/>
-      <c r="K225" s="6" t="inlineStr">
+      <c r="J145" s="2" t="inlineStr"/>
+      <c r="K145" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="5" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/ביהפר-לקטול-אבקת-חלב-לגורי-כלבים-500-גרם/</t>
         </is>
       </c>
-      <c r="B226" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C226" s="2" t="inlineStr">
+      <c r="B146" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D226" s="2" t="inlineStr"/>
-      <c r="E226" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F226" s="2" t="n">
+      <c r="D146" s="2" t="inlineStr"/>
+      <c r="E146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G226" s="5" t="inlineStr">
+      <c r="G146" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/תחליפי-חלב-לגורים/?nf_brands=ביהפר</t>
         </is>
       </c>
-      <c r="H226" s="2" t="inlineStr">
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I226" s="2" t="inlineStr">
+      <c r="I146" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J226" s="2" t="inlineStr"/>
-      <c r="K226" s="6" t="inlineStr">
+      <c r="J146" s="2" t="inlineStr"/>
+      <c r="K146" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="5" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/ביל-גק-חטיף-לכלבים-בטעם-חמאת-בוטנים-ו-2/</t>
         </is>
       </c>
-      <c r="B227" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C227" s="2" t="inlineStr">
+      <c r="B147" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D227" s="2" t="inlineStr"/>
-      <c r="E227" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F227" s="2" t="n">
+      <c r="D147" s="2" t="inlineStr"/>
+      <c r="E147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G227" s="5" t="inlineStr">
+      <c r="G147" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/כלבים/treats-bones-for-dogs/dog-treats/
 https://zoolu.co.il/product-category/חטיפים-קבוצת-מילטין/?nf_brands=bil-jac</t>
         </is>
       </c>
-      <c r="H227" s="2" t="inlineStr">
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I227" s="2" t="inlineStr">
+      <c r="I147" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J227" s="2" t="inlineStr"/>
-      <c r="K227" s="6" t="inlineStr">
+      <c r="J147" s="2" t="inlineStr"/>
+      <c r="K147" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="5" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/פטסייף-קולר-לחתול-מגנט-לדלת-פטסייף/</t>
         </is>
       </c>
-      <c r="B228" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C228" s="2" t="inlineStr">
+      <c r="B148" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D228" s="2" t="inlineStr"/>
-      <c r="E228" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F228" s="2" t="n">
+      <c r="D148" s="2" t="inlineStr"/>
+      <c r="E148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G228" s="5" t="inlineStr">
+      <c r="G148" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/התנהגות-וחינוך/
 https://zoolu.co.il/product/פטסייף-קולר-לחתול-מגנט-לדלת-פטסייף/</t>
         </is>
       </c>
-      <c r="H228" s="2" t="inlineStr">
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I228" s="2" t="inlineStr">
+      <c r="I148" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J228" s="2" t="inlineStr"/>
-      <c r="K228" s="6" t="inlineStr">
+      <c r="J148" s="2" t="inlineStr"/>
+      <c r="K148" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="5" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/סימבה-שימור-פניניות-לחתול-400-גרם/</t>
         </is>
       </c>
-      <c r="B229" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C229" s="2" t="inlineStr">
+      <c r="B149" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D229" s="2" t="inlineStr"/>
-      <c r="E229" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F229" s="2" t="n">
+      <c r="D149" s="2" t="inlineStr"/>
+      <c r="E149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G229" s="5" t="inlineStr">
+      <c r="G149" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/?utm_source=chatgpt.com</t>
         </is>
       </c>
-      <c r="H229" s="2" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I229" s="2" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J229" s="2" t="inlineStr"/>
-      <c r="K229" s="6" t="inlineStr">
+      <c r="J149" s="2" t="inlineStr"/>
+      <c r="K149" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="5" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/hivt-mhmd-bzmn-hirvm-tipim-ltipvl-vhrgeh/</t>
         </is>
       </c>
-      <c r="B230" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C230" s="2" t="inlineStr">
+      <c r="B150" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D230" s="2" t="inlineStr"/>
-      <c r="E230" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F230" s="2" t="n">
+      <c r="D150" s="2" t="inlineStr"/>
+      <c r="E150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G230" s="2" t="inlineStr"/>
-      <c r="H230" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I230" s="2" t="inlineStr">
+      <c r="I150" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J230" s="2" t="inlineStr"/>
-      <c r="K230" s="6" t="inlineStr">
+      <c r="J150" s="2" t="inlineStr"/>
+      <c r="K150" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="5" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/אקווטיקה/?nf_brands=קוקו-chicos</t>
         </is>
       </c>
-      <c r="B231" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C231" s="2" t="inlineStr">
+      <c r="B151" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D231" s="2" t="inlineStr"/>
-      <c r="E231" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F231" s="2" t="n">
+      <c r="D151" s="2" t="inlineStr"/>
+      <c r="E151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G231" s="2" t="inlineStr"/>
-      <c r="H231" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I231" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J231" s="2" t="inlineStr"/>
-      <c r="K231" s="6" t="inlineStr">
+      <c r="J151" s="2" t="inlineStr"/>
+      <c r="K151" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="5" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/jbl-טסט-חדש-לבדיקת-חמצן-במים-o2/</t>
         </is>
       </c>
-      <c r="B232" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C232" s="2" t="inlineStr">
+      <c r="B152" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D232" s="2" t="inlineStr"/>
-      <c r="E232" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F232" s="2" t="n">
+      <c r="D152" s="2" t="inlineStr"/>
+      <c r="E152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G232" s="5" t="inlineStr">
+      <c r="G152" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/jbl-טסט-חדש-לבדיקת-חמצן-במים-o2/
 https://zoolu.co.il/product/jbl-פרו-נובו-טאב-טבליות-250-מל-m/
@@ -35491,246 +32203,246 @@
 https://zoolu.co.il/product/דקורציה-רדיו-היפי-צבעוני-במידה-12x5x9-סמ/</t>
         </is>
       </c>
-      <c r="H232" s="2" t="inlineStr">
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I232" s="2" t="inlineStr">
+      <c r="I152" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J232" s="2" t="inlineStr"/>
-      <c r="K232" s="6" t="inlineStr">
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="5" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/jbl-פרו-נובו-טנגניקה-ציקליד-מגורען-250-מל-m/</t>
         </is>
       </c>
-      <c r="B233" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C233" s="2" t="inlineStr">
+      <c r="B153" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D233" s="2" t="inlineStr"/>
-      <c r="E233" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F233" s="2" t="n">
+      <c r="D153" s="2" t="inlineStr"/>
+      <c r="E153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G233" s="5" t="inlineStr">
+      <c r="G153" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/jbl-מזון-בריכות-פרופונד-מיקס-כל-העונות-0-8-ק/
 https://zoolu.co.il/product/jbl-פרו-נובו-בל-דפים-250מל-m/
 https://zoolu.co.il/product-category/תזונה-קבוצת-מילטין/</t>
         </is>
       </c>
-      <c r="H233" s="2" t="inlineStr">
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I233" s="2" t="inlineStr">
+      <c r="I153" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J233" s="2" t="inlineStr"/>
-      <c r="K233" s="6" t="inlineStr">
+      <c r="J153" s="2" t="inlineStr"/>
+      <c r="K153" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="5" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/אקווטיקה/?nf_brands=מרינה</t>
         </is>
       </c>
-      <c r="B234" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C234" s="2" t="inlineStr">
+      <c r="B154" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D234" s="2" t="inlineStr"/>
-      <c r="E234" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F234" s="2" t="n">
+      <c r="D154" s="2" t="inlineStr"/>
+      <c r="E154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G234" s="2" t="inlineStr"/>
-      <c r="H234" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I234" s="2" t="inlineStr">
+      <c r="I154" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J234" s="2" t="inlineStr"/>
-      <c r="K234" s="6" t="inlineStr">
+      <c r="J154" s="2" t="inlineStr"/>
+      <c r="K154" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="5" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/אקווטיקה/?nf_brands=אקוואטלנטיס</t>
         </is>
       </c>
-      <c r="B235" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C235" s="2" t="inlineStr">
+      <c r="B155" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D235" s="2" t="inlineStr"/>
-      <c r="E235" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F235" s="2" t="n">
+      <c r="D155" s="2" t="inlineStr"/>
+      <c r="E155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G235" s="2" t="inlineStr"/>
-      <c r="H235" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I235" s="2" t="inlineStr">
+      <c r="I155" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J235" s="2" t="inlineStr"/>
-      <c r="K235" s="6" t="inlineStr">
+      <c r="J155" s="2" t="inlineStr"/>
+      <c r="K155" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="5" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/אקווטיקה/?nf_brands=נוטרפין</t>
         </is>
       </c>
-      <c r="B236" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C236" s="2" t="inlineStr">
+      <c r="B156" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D236" s="2" t="inlineStr"/>
-      <c r="E236" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F236" s="2" t="n">
+      <c r="D156" s="2" t="inlineStr"/>
+      <c r="E156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G236" s="2" t="inlineStr"/>
-      <c r="H236" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I236" s="2" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J236" s="2" t="inlineStr"/>
-      <c r="K236" s="6" t="inlineStr">
+      <c r="J156" s="2" t="inlineStr"/>
+      <c r="K156" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="5" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/אהיים-פילטר-פנימי-פאוור-ליין-200/</t>
         </is>
       </c>
-      <c r="B237" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C237" s="2" t="inlineStr">
+      <c r="B157" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D237" s="2" t="inlineStr"/>
-      <c r="E237" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F237" s="2" t="n">
+      <c r="D157" s="2" t="inlineStr"/>
+      <c r="E157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G237" s="2" t="inlineStr"/>
-      <c r="H237" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I237" s="2" t="inlineStr">
+      <c r="I157" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J237" s="2" t="inlineStr"/>
-      <c r="K237" s="6" t="inlineStr">
+      <c r="J157" s="2" t="inlineStr"/>
+      <c r="K157" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="5" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/מברשת-לפרווה-עם-אדים-חשמלית-6-51120-סמ/</t>
         </is>
       </c>
-      <c r="B238" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C238" s="2" t="inlineStr">
+      <c r="B158" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D238" s="2" t="inlineStr"/>
-      <c r="E238" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F238" s="2" t="n">
+      <c r="D158" s="2" t="inlineStr"/>
+      <c r="E158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G238" s="5" t="inlineStr">
+      <c r="G158" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/cats/cat-grooming-products/
 https://zoolu.co.il/product-category/כלבים/dog-grooming-products/dog-brushes-combs/
@@ -35739,90 +32451,90 @@
 https://zoolu.co.il/product-category/מברשות-ומסרקים/</t>
         </is>
       </c>
-      <c r="H238" s="2" t="inlineStr">
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I238" s="2" t="inlineStr">
+      <c r="I158" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J238" s="2" t="inlineStr"/>
-      <c r="K238" s="6" t="inlineStr">
+      <c r="J158" s="2" t="inlineStr"/>
+      <c r="K158" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="5" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/תכשיר-ניקוי-אנזימטי-לאוזניים-118-מל-הום/</t>
         </is>
       </c>
-      <c r="B239" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C239" s="2" t="inlineStr">
+      <c r="B159" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D239" s="2" t="inlineStr"/>
-      <c r="E239" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F239" s="2" t="n">
+      <c r="D159" s="2" t="inlineStr"/>
+      <c r="E159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G239" s="5" t="inlineStr">
+      <c r="G159" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/cats/cat-grooming-products/
 https://zoolu.co.il/product/תכשיר-שטיפת-עיניים-להרגעה-18-מל-של-הום-ו/
 https://zoolu.co.il/product/מגבונים-לחים-לניקוי-אזניים-50-יח-של-אוק/</t>
         </is>
       </c>
-      <c r="H239" s="2" t="inlineStr">
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I239" s="2" t="inlineStr">
+      <c r="I159" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J239" s="2" t="inlineStr"/>
-      <c r="K239" s="6" t="inlineStr">
+      <c r="J159" s="2" t="inlineStr"/>
+      <c r="K159" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="5" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/מברשת-דו-צדדית-שחור-אפור-l-של-חברת-devo/</t>
         </is>
       </c>
-      <c r="B240" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C240" s="2" t="inlineStr">
+      <c r="B160" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D240" s="2" t="inlineStr"/>
-      <c r="E240" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F240" s="2" t="n">
+      <c r="D160" s="2" t="inlineStr"/>
+      <c r="E160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G240" s="5" t="inlineStr">
+      <c r="G160" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/cats/cat-grooming-products/
 https://zoolu.co.il/product-category/כלבים/dog-grooming-products/dog-brushes-combs/
@@ -35836,84 +32548,84 @@
 https://zoolu.co.il/product-category/מברשות-ומסרקים/</t>
         </is>
       </c>
-      <c r="H240" s="2" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I240" s="2" t="inlineStr">
+      <c r="I160" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J240" s="2" t="inlineStr"/>
-      <c r="K240" s="6" t="inlineStr">
+      <c r="J160" s="2" t="inlineStr"/>
+      <c r="K160" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="5" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/cats/cat-grooming-products/?nf_brands=איי-דוג</t>
         </is>
       </c>
-      <c r="B241" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C241" s="2" t="inlineStr">
+      <c r="B161" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D241" s="2" t="inlineStr"/>
-      <c r="E241" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F241" s="2" t="n">
+      <c r="D161" s="2" t="inlineStr"/>
+      <c r="E161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G241" s="2" t="inlineStr"/>
-      <c r="H241" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I241" s="2" t="inlineStr">
+      <c r="I161" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J241" s="2" t="inlineStr"/>
-      <c r="K241" s="6" t="inlineStr">
+      <c r="J161" s="2" t="inlineStr"/>
+      <c r="K161" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="5" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/לה-סלון-קוצץ-ציפורניים-מקצועי-קאטר-לכ/</t>
         </is>
       </c>
-      <c r="B242" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C242" s="2" t="inlineStr">
+      <c r="B162" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D242" s="2" t="inlineStr"/>
-      <c r="E242" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F242" s="2" t="n">
+      <c r="D162" s="2" t="inlineStr"/>
+      <c r="E162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G242" s="5" t="inlineStr">
+      <c r="G162" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/cats/cat-grooming-products/
 https://zoolu.co.il/product-category/cats/cat-grooming-products/?nf_brands=לה-סלון
@@ -35921,262 +32633,262 @@
 https://zoolu.co.il/product-category/קוצצי-ציפורניים/</t>
         </is>
       </c>
-      <c r="H242" s="2" t="inlineStr">
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I242" s="2" t="inlineStr">
+      <c r="I162" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J242" s="2" t="inlineStr"/>
-      <c r="K242" s="6" t="inlineStr">
+      <c r="J162" s="2" t="inlineStr"/>
+      <c r="K162" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="5" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/פלקסי-רצועה-נמתחת-לגור-כלבים-2-מטר/</t>
         </is>
       </c>
-      <c r="B243" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C243" s="2" t="inlineStr">
+      <c r="B163" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D243" s="2" t="inlineStr"/>
-      <c r="E243" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F243" s="2" t="n">
+      <c r="D163" s="2" t="inlineStr"/>
+      <c r="E163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G243" s="5" t="inlineStr">
+      <c r="G163" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/פלקסי-רצועה-נמתחת-לגור-כלבים-2-מטר/</t>
         </is>
       </c>
-      <c r="H243" s="2" t="inlineStr">
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I243" s="2" t="inlineStr">
+      <c r="I163" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J243" s="2" t="inlineStr"/>
-      <c r="K243" s="6" t="inlineStr">
+      <c r="J163" s="2" t="inlineStr"/>
+      <c r="K163" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" s="5" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/פלקסי-ניו-נאון-ירוק-ושחור-רצועה-נמתחת/</t>
         </is>
       </c>
-      <c r="B244" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C244" s="2" t="inlineStr">
+      <c r="B164" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D244" s="2" t="inlineStr"/>
-      <c r="E244" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F244" s="2" t="n">
+      <c r="D164" s="2" t="inlineStr"/>
+      <c r="E164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G244" s="5" t="inlineStr">
+      <c r="G164" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/פלקסי-ניו-נאון-ירוק-ושחור-רצועה-נמתחת/</t>
         </is>
       </c>
-      <c r="H244" s="2" t="inlineStr">
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I244" s="2" t="inlineStr">
+      <c r="I164" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J244" s="2" t="inlineStr"/>
-      <c r="K244" s="6" t="inlineStr">
+      <c r="J164" s="2" t="inlineStr"/>
+      <c r="K164" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="5" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/פלקסי-אקסטרים-כתום-ושחור-רצועה-נמתחת-ל-3/</t>
         </is>
       </c>
-      <c r="B245" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C245" s="2" t="inlineStr">
+      <c r="B165" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D245" s="2" t="inlineStr"/>
-      <c r="E245" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F245" s="2" t="n">
+      <c r="D165" s="2" t="inlineStr"/>
+      <c r="E165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F165" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G245" s="5" t="inlineStr">
+      <c r="G165" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/פלקסי-אקסטרים-כתום-ושחור-רצועה-נמתחת-ל-3/</t>
         </is>
       </c>
-      <c r="H245" s="2" t="inlineStr">
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I245" s="2" t="inlineStr">
+      <c r="I165" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J245" s="2" t="inlineStr"/>
-      <c r="K245" s="6" t="inlineStr">
+      <c r="J165" s="2" t="inlineStr"/>
+      <c r="K165" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="5" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/פלקסי-רצועה-נמתחת-לגור-כלבים-2-מטר-2/</t>
         </is>
       </c>
-      <c r="B246" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C246" s="2" t="inlineStr">
+      <c r="B166" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D246" s="2" t="inlineStr"/>
-      <c r="E246" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F246" s="2" t="n">
+      <c r="D166" s="2" t="inlineStr"/>
+      <c r="E166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G246" s="5" t="inlineStr">
+      <c r="G166" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/פלקסי-רצועה-נמתחת-לגור-כלבים-2-מטר-2/</t>
         </is>
       </c>
-      <c r="H246" s="2" t="inlineStr">
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I246" s="2" t="inlineStr">
+      <c r="I166" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J246" s="2" t="inlineStr"/>
-      <c r="K246" s="6" t="inlineStr">
+      <c r="J166" s="2" t="inlineStr"/>
+      <c r="K166" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="5" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/ליווינג-וורלד-כלי-אוכל-פנימי-לציפורים-2/</t>
         </is>
       </c>
-      <c r="B247" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C247" s="2" t="inlineStr">
+      <c r="B167" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D247" s="2" t="inlineStr"/>
-      <c r="E247" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F247" s="2" t="n">
+      <c r="D167" s="2" t="inlineStr"/>
+      <c r="E167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G247" s="5" t="inlineStr">
+      <c r="G167" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/ציפורים/bird-equipment/
 https://zoolu.co.il/product/ליווינג-וורלד-כלי-אוכל-פנימי-לציפורים-3/
 https://zoolu.co.il/product/ליווינג-וורלד-זוג-כלי-מים-ומזון-קטנים/</t>
         </is>
       </c>
-      <c r="H247" s="2" t="inlineStr">
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I247" s="2" t="inlineStr">
+      <c r="I167" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J247" s="2" t="inlineStr"/>
-      <c r="K247" s="6" t="inlineStr">
+      <c r="J167" s="2" t="inlineStr"/>
+      <c r="K167" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="5" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/קיט-קט-חול-סויה-מתגבש-אוריגינל-7-ליטר/</t>
         </is>
       </c>
-      <c r="B248" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C248" s="2" t="inlineStr">
+      <c r="B168" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D248" s="2" t="inlineStr"/>
-      <c r="E248" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F248" s="2" t="n">
+      <c r="D168" s="2" t="inlineStr"/>
+      <c r="E168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G248" s="5" t="inlineStr">
+      <c r="G168" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/sales/?nf_brands=קיט-קט
 https://zoolu.co.il/product/קיט-קט-חול-סויה-מתגבש-אוריגינל-7-ליטר/
@@ -36184,476 +32896,476 @@
 https://zoolu.co.il/product-category/חולות-קבוצת-מילטין/</t>
         </is>
       </c>
-      <c r="H248" s="2" t="inlineStr">
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I248" s="2" t="inlineStr">
+      <c r="I168" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J248" s="2" t="inlineStr"/>
-      <c r="K248" s="6" t="inlineStr">
+      <c r="J168" s="2" t="inlineStr"/>
+      <c r="K168" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="5" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/rodents/rodent-equipment-accessories/?nf_brands=ליוינג-וורלד</t>
         </is>
       </c>
-      <c r="B249" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C249" s="2" t="inlineStr">
+      <c r="B169" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D249" s="2" t="inlineStr"/>
-      <c r="E249" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F249" s="2" t="n">
+      <c r="D169" s="2" t="inlineStr"/>
+      <c r="E169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G249" s="2" t="inlineStr"/>
-      <c r="H249" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I249" s="2" t="inlineStr">
+      <c r="I169" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J249" s="2" t="inlineStr"/>
-      <c r="K249" s="6" t="inlineStr">
+      <c r="J169" s="2" t="inlineStr"/>
+      <c r="K169" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="5" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/דקורציה-וואן-היפי-צבעוני-במידה-13x6x6-סמ/</t>
         </is>
       </c>
-      <c r="B250" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C250" s="2" t="inlineStr">
+      <c r="B170" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D250" s="2" t="inlineStr"/>
-      <c r="E250" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F250" s="2" t="n">
+      <c r="D170" s="2" t="inlineStr"/>
+      <c r="E170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G250" s="5" t="inlineStr">
+      <c r="G170" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/דקורציה-וואן-היפי-צבעוני-במידה-13x6x6-סמ/</t>
         </is>
       </c>
-      <c r="H250" s="2" t="inlineStr">
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I250" s="2" t="inlineStr">
+      <c r="I170" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J250" s="2" t="inlineStr"/>
-      <c r="K250" s="6" t="inlineStr">
+      <c r="J170" s="2" t="inlineStr"/>
+      <c r="K170" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="5" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/דקורציה/?nf_brands=imac</t>
         </is>
       </c>
-      <c r="B251" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C251" s="2" t="inlineStr">
+      <c r="B171" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D251" s="2" t="inlineStr"/>
-      <c r="E251" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F251" s="2" t="n">
+      <c r="D171" s="2" t="inlineStr"/>
+      <c r="E171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G251" s="5" t="inlineStr">
+      <c r="G171" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/דקורציה/?nf_brands=גי-בי-אל-jbl
 https://zoolu.co.il/product-category/דקורציה/?nf_brands=imac</t>
         </is>
       </c>
-      <c r="H251" s="2" t="inlineStr">
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I251" s="2" t="inlineStr">
+      <c r="I171" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J251" s="2" t="inlineStr"/>
-      <c r="K251" s="6" t="inlineStr">
+      <c r="J171" s="2" t="inlineStr"/>
+      <c r="K171" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" s="5" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/דקורציה-מערת-קינון-לזוחלים-בצורת-עץ-20x20x11/</t>
         </is>
       </c>
-      <c r="B252" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C252" s="2" t="inlineStr">
+      <c r="B172" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D252" s="2" t="inlineStr"/>
-      <c r="E252" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F252" s="2" t="n">
+      <c r="D172" s="2" t="inlineStr"/>
+      <c r="E172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F172" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G252" s="5" t="inlineStr">
+      <c r="G172" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/דקורציה-מערת-קינון-לזוחלים-בצורת-עץ-15-5x15x8/
 https://zoolu.co.il/product/דקורציה-מערת-קינון-לזוחלים-בצורת-עץ-30-5x30-5x13/
 https://zoolu.co.il/product/דקורציה-מערת-קינון-לזוחלים-בצורת-עץ-20x20x11/</t>
         </is>
       </c>
-      <c r="H252" s="2" t="inlineStr">
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I252" s="2" t="inlineStr">
+      <c r="I172" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J252" s="2" t="inlineStr"/>
-      <c r="K252" s="6" t="inlineStr">
+      <c r="J172" s="2" t="inlineStr"/>
+      <c r="K172" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" s="5" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/כלבים/dog-pest-control/?nf_brands=ab7</t>
         </is>
       </c>
-      <c r="B253" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C253" s="2" t="inlineStr">
+      <c r="B173" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D253" s="2" t="inlineStr"/>
-      <c r="E253" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F253" s="2" t="n">
+      <c r="D173" s="2" t="inlineStr"/>
+      <c r="E173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G253" s="5" t="inlineStr">
+      <c r="G173" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/כלבים/dog-pest-control/?nf_brands=טרופיקלין
 https://zoolu.co.il/product-category/כלבים/dog-pest-control/?nf_brands=בימדה-bimeda</t>
         </is>
       </c>
-      <c r="H253" s="2" t="inlineStr">
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I253" s="2" t="inlineStr">
+      <c r="I173" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J253" s="2" t="inlineStr"/>
-      <c r="K253" s="6" t="inlineStr">
+      <c r="J173" s="2" t="inlineStr"/>
+      <c r="K173" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" s="5" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/גוסרה-הלפ-מזון-טיפולי-הארט-לכלבים-10-ק/</t>
         </is>
       </c>
-      <c r="B254" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C254" s="2" t="inlineStr">
+      <c r="B174" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D254" s="2" t="inlineStr"/>
-      <c r="E254" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F254" s="2" t="n">
+      <c r="D174" s="2" t="inlineStr"/>
+      <c r="E174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G254" s="5" t="inlineStr">
+      <c r="G174" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/גוסרה-הלפ-מזון-טיפולי-הארט-לכלבים-10-ק/</t>
         </is>
       </c>
-      <c r="H254" s="2" t="inlineStr">
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I254" s="2" t="inlineStr">
+      <c r="I174" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J254" s="2" t="inlineStr"/>
-      <c r="K254" s="6" t="inlineStr">
+      <c r="J174" s="2" t="inlineStr"/>
+      <c r="K174" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" s="5" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/גוסרה-מזון-יבש-ללא-דגנים-לכלבים-בוגרי-2/</t>
         </is>
       </c>
-      <c r="B255" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C255" s="2" t="inlineStr">
+      <c r="B175" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D255" s="2" t="inlineStr"/>
-      <c r="E255" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F255" s="2" t="n">
+      <c r="D175" s="2" t="inlineStr"/>
+      <c r="E175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G255" s="5" t="inlineStr">
+      <c r="G175" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/גוסרה-מזון-יבש-ללא-דגנים-לכלבים-בוגרי-2/</t>
         </is>
       </c>
-      <c r="H255" s="2" t="inlineStr">
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I255" s="2" t="inlineStr">
+      <c r="I175" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J255" s="2" t="inlineStr"/>
-      <c r="K255" s="6" t="inlineStr">
+      <c r="J175" s="2" t="inlineStr"/>
+      <c r="K175" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" s="5" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/ונפי-חטיף-דנטלי-לכלב-מברשת-שיניים-בטע/</t>
         </is>
       </c>
-      <c r="B256" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C256" s="2" t="inlineStr">
+      <c r="B176" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D256" s="2" t="inlineStr"/>
-      <c r="E256" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F256" s="2" t="n">
+      <c r="D176" s="2" t="inlineStr"/>
+      <c r="E176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G256" s="5" t="inlineStr">
+      <c r="G176" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/ונפי-חטיף-דנטלי-לכלב-מברשת-שיניים-בטע/</t>
         </is>
       </c>
-      <c r="H256" s="2" t="inlineStr">
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I256" s="2" t="inlineStr">
+      <c r="I176" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J256" s="2" t="inlineStr"/>
-      <c r="K256" s="6" t="inlineStr">
+      <c r="J176" s="2" t="inlineStr"/>
+      <c r="K176" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="5" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/סולו-חטיף-נגיסי-עוף-לכלבים-80-גרם/</t>
         </is>
       </c>
-      <c r="B257" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C257" s="2" t="inlineStr">
+      <c r="B177" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D257" s="2" t="inlineStr"/>
-      <c r="E257" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F257" s="2" t="n">
+      <c r="D177" s="2" t="inlineStr"/>
+      <c r="E177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G257" s="5" t="inlineStr">
+      <c r="G177" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/כלבים/treats-bones-for-dogs/dog-treats/</t>
         </is>
       </c>
-      <c r="H257" s="2" t="inlineStr">
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I257" s="2" t="inlineStr">
+      <c r="I177" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J257" s="2" t="inlineStr"/>
-      <c r="K257" s="6" t="inlineStr">
+      <c r="J177" s="2" t="inlineStr"/>
+      <c r="K177" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" s="5" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/ביל-גק-חטיף-לכלבים-בטעם-חמאת-בוטנים-283/</t>
         </is>
       </c>
-      <c r="B258" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C258" s="2" t="inlineStr">
+      <c r="B178" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D258" s="2" t="inlineStr"/>
-      <c r="E258" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F258" s="2" t="n">
+      <c r="D178" s="2" t="inlineStr"/>
+      <c r="E178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G258" s="5" t="inlineStr">
+      <c r="G178" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/כלבים/treats-bones-for-dogs/dog-treats/
 https://zoolu.co.il/product-category/חטיפים-קבוצת-מילטין/?nf_brands=bil-jac</t>
         </is>
       </c>
-      <c r="H258" s="2" t="inlineStr">
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I258" s="2" t="inlineStr">
+      <c r="I178" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J258" s="2" t="inlineStr"/>
-      <c r="K258" s="6" t="inlineStr">
+      <c r="J178" s="2" t="inlineStr"/>
+      <c r="K178" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" s="5" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/חטיפים-קבוצת-מילטין/?nf_brands=prama</t>
         </is>
       </c>
-      <c r="B259" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C259" s="2" t="inlineStr">
+      <c r="B179" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D259" s="2" t="inlineStr"/>
-      <c r="E259" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F259" s="2" t="n">
+      <c r="D179" s="2" t="inlineStr"/>
+      <c r="E179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F179" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G259" s="5" t="inlineStr">
+      <c r="G179" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/חטיפים-קבוצת-מילטין/?nf_brands=odog
 https://zoolu.co.il/product-category/חטיפים-קבוצת-מילטין/?nf_brands=זאוס
@@ -36668,188 +33380,188 @@
 (ועוד 3)</t>
         </is>
       </c>
-      <c r="H259" s="2" t="inlineStr">
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I259" s="2" t="inlineStr">
+      <c r="I179" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J259" s="2" t="inlineStr"/>
-      <c r="K259" s="6" t="inlineStr">
+      <c r="J179" s="2" t="inlineStr"/>
+      <c r="K179" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="5" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/סולו-בשר-עוף-מגולגל-על-מקל-עור-לכלבים-80/</t>
         </is>
       </c>
-      <c r="B260" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C260" s="2" t="inlineStr">
+      <c r="B180" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D260" s="2" t="inlineStr"/>
-      <c r="E260" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F260" s="2" t="n">
+      <c r="D180" s="2" t="inlineStr"/>
+      <c r="E180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G260" s="5" t="inlineStr">
+      <c r="G180" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/כלבים/treats-bones-for-dogs/dog-treats/</t>
         </is>
       </c>
-      <c r="H260" s="2" t="inlineStr">
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I260" s="2" t="inlineStr">
+      <c r="I180" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J260" s="2" t="inlineStr"/>
-      <c r="K260" s="6" t="inlineStr">
+      <c r="J180" s="2" t="inlineStr"/>
+      <c r="K180" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" s="5" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/חטיפים-קבוצת-מילטין/?nf_brands=ויסקאס</t>
         </is>
       </c>
-      <c r="B261" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C261" s="2" t="inlineStr">
+      <c r="B181" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D261" s="2" t="inlineStr"/>
-      <c r="E261" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F261" s="2" t="n">
+      <c r="D181" s="2" t="inlineStr"/>
+      <c r="E181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G261" s="2" t="inlineStr"/>
-      <c r="H261" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I261" s="2" t="inlineStr">
+      <c r="I181" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J261" s="2" t="inlineStr"/>
-      <c r="K261" s="6" t="inlineStr">
+      <c r="J181" s="2" t="inlineStr"/>
+      <c r="K181" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" s="5" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product/ציקופט-טיטולים-לכלבות-נקבות-63-76-סמ-מידה-xl/</t>
         </is>
       </c>
-      <c r="B262" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C262" s="2" t="inlineStr">
+      <c r="B182" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D262" s="2" t="inlineStr"/>
-      <c r="E262" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F262" s="2" t="n">
+      <c r="D182" s="2" t="inlineStr"/>
+      <c r="E182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G262" s="5" t="inlineStr">
+      <c r="G182" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/כלבים/home-and-environment-for-dogs/miscellaneous-for-dogs/
 https://zoolu.co.il/product-category/התנהגות-וחינוך/
 https://zoolu.co.il/product/דוקטרא-קולר-אילוף-1200-1900arc/</t>
         </is>
       </c>
-      <c r="H262" s="2" t="inlineStr">
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I262" s="2" t="inlineStr">
+      <c r="I182" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J262" s="2" t="inlineStr"/>
-      <c r="K262" s="6" t="inlineStr">
+      <c r="J182" s="2" t="inlineStr"/>
+      <c r="K182" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" s="5" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/אקווטיקה/page/7/</t>
         </is>
       </c>
-      <c r="B263" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="C263" s="2" t="inlineStr">
+      <c r="B183" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
         <is>
           <t>429 -&gt; 200</t>
         </is>
       </c>
-      <c r="D263" s="2" t="inlineStr"/>
-      <c r="E263" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F263" s="2" t="n">
+      <c r="D183" s="2" t="inlineStr"/>
+      <c r="E183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F183" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G263" s="5" t="inlineStr">
+      <c r="G183" s="5" t="inlineStr">
         <is>
           <t>https://zoolu.co.il/product-category/אקווטיקה/page/6/</t>
         </is>
       </c>
-      <c r="H263" s="2" t="inlineStr">
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק שאומתו כתקינות</t>
         </is>
       </c>
-      <c r="I263" s="2" t="inlineStr">
+      <c r="I183" s="2" t="inlineStr">
         <is>
           <t>בסריקה מ-23.09 הסורק הוגבל (קוד 429); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
         </is>
       </c>
-      <c r="J263" s="2" t="inlineStr"/>
-      <c r="K263" s="6" t="inlineStr">
+      <c r="J183" s="2" t="inlineStr"/>
+      <c r="K183" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>

--- a/public/crawlability-zoolu-september-2026.xlsx
+++ b/public/crawlability-zoolu-september-2026.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -502,7 +502,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>להסיר רשומה כפולה אחת ממפת האתר.</t>
+          <t>staging.zoolu.co.il: תת-הדומיין קיים ומחזיר עמוד אימות של Cloudflare (429, noindex) לסורקים. לוודא שההגנה נשארת פעילה; לא נמצא באינדקס.</t>
         </is>
       </c>
     </row>
@@ -510,57 +510,12 @@
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>לבדיקה</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>staging.zoolu.co.il: תת-הדומיין קיים ומחזיר עמוד אימות של Cloudflare (429, noindex) לסורקים. לוודא שההגנה נשארת פעילה; לא נמצא באינדקס.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>להריץ מחדש (בממשק) את ה-Website Audit של zoolu ב-SE Ranking; הסריקה האחרונה: 2026-04-03.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>לבדיקה</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>לאשר ש-7 העמודים המוגדרים noindex אכן אמורים להישאר מחוץ לאינדקס.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>לבדיקה</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>חסימות סורק (403/429/timeout) לבדיקה: 523 כתובות; הבולטת https://zoolu.co.il/product-category/כלבים/home-and-environment-for-dogs/dog-ken… (76 קישורים נכנסים).</t>
         </is>
